--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,32 +1427,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121004536</v>
+        <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>81312</v>
+        <v>92675</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,17 +1461,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550477</v>
+        <v>550489</v>
       </c>
       <c r="R9" t="n">
-        <v>6994042</v>
+        <v>6993892</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/136674026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004550</v>
+        <v>121004536</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550508</v>
+        <v>550477</v>
       </c>
       <c r="R10" t="n">
-        <v>6994113</v>
+        <v>6994042</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1633,13 +1633,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126099520</v>
+        <v>121004550</v>
       </c>
       <c r="B11" t="n">
         <v>81312</v>
@@ -1673,14 +1673,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550419</v>
+        <v>550508</v>
       </c>
       <c r="R11" t="n">
-        <v>6994207</v>
+        <v>6994113</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,16 +1739,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102089224</v>
+        <v>126099520</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,35 +1756,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550562</v>
+        <v>550419</v>
       </c>
       <c r="R12" t="n">
-        <v>6994152</v>
+        <v>6994207</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,12 +1813,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1827,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1842,54 +1845,52 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121004416</v>
+        <v>102089224</v>
       </c>
       <c r="B13" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550398</v>
+        <v>550562</v>
       </c>
       <c r="R13" t="n">
-        <v>6994131</v>
+        <v>6994152</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1916,12 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,7 +1931,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1948,13 +1948,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004472</v>
+        <v>121004416</v>
       </c>
       <c r="B14" t="n">
         <v>92083</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550400</v>
+        <v>550398</v>
       </c>
       <c r="R14" t="n">
-        <v>6993983</v>
+        <v>6994131</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,38 +2054,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004362</v>
+        <v>121004472</v>
       </c>
       <c r="B15" t="n">
-        <v>90932</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550364</v>
+        <v>550400</v>
       </c>
       <c r="R15" t="n">
-        <v>6994169</v>
+        <v>6993983</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004490</v>
+        <v>121004362</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550508</v>
+        <v>550364</v>
       </c>
       <c r="R16" t="n">
-        <v>6993803</v>
+        <v>6994169</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,13 +2266,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004539</v>
+        <v>121004490</v>
       </c>
       <c r="B17" t="n">
         <v>90932</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550486</v>
+        <v>550508</v>
       </c>
       <c r="R17" t="n">
-        <v>6994062</v>
+        <v>6993803</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2372,16 +2372,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62025591</v>
+        <v>121004539</v>
       </c>
       <c r="B18" t="n">
-        <v>91962</v>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2389,37 +2389,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550409</v>
+        <v>550486</v>
       </c>
       <c r="R18" t="n">
-        <v>6994048</v>
+        <v>6994062</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,12 +2446,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,43 +2460,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102089002</v>
+        <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>80433</v>
+        <v>91111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,38 +2495,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550570</v>
+        <v>550478</v>
       </c>
       <c r="R19" t="n">
-        <v>6994156</v>
+        <v>6994127</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,17 +2549,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,51 +2580,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/136620821</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103996059</v>
+        <v>62025591</v>
       </c>
       <c r="B20" t="n">
-        <v>96338</v>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550310</v>
+        <v>550409</v>
       </c>
       <c r="R20" t="n">
-        <v>6994183</v>
+        <v>6994048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,22 +2651,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,39 +2668,40 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004351</v>
+        <v>102089002</v>
       </c>
       <c r="B21" t="n">
-        <v>91831</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,37 +2709,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3242</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550358</v>
+        <v>550570</v>
       </c>
       <c r="R21" t="n">
-        <v>6994160</v>
+        <v>6994156</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,12 +2764,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,7 +2783,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,57 +2800,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121004470</v>
+        <v>103996059</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>96338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550383</v>
+        <v>550310</v>
       </c>
       <c r="R22" t="n">
-        <v>6993994</v>
+        <v>6994183</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2893,17 +2871,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,9 +2895,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2924,22 +2911,26 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135457707</v>
+        <v>121004351</v>
       </c>
       <c r="B23" t="n">
-        <v>93354</v>
+        <v>91831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550510</v>
+        <v>550358</v>
       </c>
       <c r="R23" t="n">
-        <v>6993821</v>
+        <v>6994160</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3004,12 +2995,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,16 +3027,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457707</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62025592</v>
+        <v>121004470</v>
       </c>
       <c r="B24" t="n">
-        <v>93197</v>
+        <v>91831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,37 +3044,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550409</v>
+        <v>550383</v>
       </c>
       <c r="R24" t="n">
-        <v>6994048</v>
+        <v>6993994</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3107,12 +3101,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,43 +3120,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102089700</v>
+        <v>135457707</v>
       </c>
       <c r="B25" t="n">
-        <v>93197</v>
+        <v>93354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,35 +3155,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550476</v>
+        <v>550510</v>
       </c>
       <c r="R25" t="n">
-        <v>6994117</v>
+        <v>6993821</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3220,12 +3212,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,6 +3226,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3251,13 +3244,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/135457707</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103996072</v>
+        <v>62025592</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3288,14 +3281,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550481</v>
+        <v>550409</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994048</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,22 +3315,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3349,36 +3332,37 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103996080</v>
+        <v>102089700</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3407,19 +3391,20 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550485</v>
+        <v>550476</v>
       </c>
       <c r="R27" t="n">
-        <v>6994105</v>
+        <v>6994117</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3443,22 +3428,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3469,11 +3444,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3483,23 +3453,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121004341</v>
+        <v>103996072</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3528,22 +3494,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550344</v>
+        <v>550481</v>
       </c>
       <c r="R28" t="n">
-        <v>6994160</v>
+        <v>6994068</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3567,12 +3530,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3581,9 +3554,13 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3593,19 +3570,23 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121004394</v>
+        <v>103996080</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3634,22 +3615,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550381</v>
+        <v>550485</v>
       </c>
       <c r="R29" t="n">
-        <v>6994155</v>
+        <v>6994105</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,12 +3651,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3687,9 +3675,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3699,19 +3691,23 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004399</v>
+        <v>121004341</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3749,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550384</v>
+        <v>550344</v>
       </c>
       <c r="R30" t="n">
-        <v>6994151</v>
+        <v>6994160</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3811,13 +3807,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004430</v>
+        <v>121004394</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3855,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550422</v>
+        <v>550381</v>
       </c>
       <c r="R31" t="n">
-        <v>6994093</v>
+        <v>6994155</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3917,13 +3913,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004475</v>
+        <v>121004399</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3961,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550385</v>
+        <v>550384</v>
       </c>
       <c r="R32" t="n">
-        <v>6993920</v>
+        <v>6994151</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4023,13 +4019,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004484</v>
+        <v>121004430</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4067,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550427</v>
+        <v>550422</v>
       </c>
       <c r="R33" t="n">
-        <v>6993867</v>
+        <v>6994093</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4129,13 +4125,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004500</v>
+        <v>121004475</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4173,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550496</v>
+        <v>550385</v>
       </c>
       <c r="R34" t="n">
-        <v>6993817</v>
+        <v>6993920</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4235,13 +4231,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004509</v>
+        <v>121004484</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4279,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550476</v>
+        <v>550427</v>
       </c>
       <c r="R35" t="n">
-        <v>6993841</v>
+        <v>6993867</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4341,13 +4337,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004524</v>
+        <v>121004500</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4385,10 +4381,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550502</v>
+        <v>550496</v>
       </c>
       <c r="R36" t="n">
-        <v>6993935</v>
+        <v>6993817</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4447,13 +4443,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004537</v>
+        <v>121004509</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4491,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550477</v>
+        <v>550476</v>
       </c>
       <c r="R37" t="n">
-        <v>6994042</v>
+        <v>6993841</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4553,13 +4549,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004540</v>
+        <v>121004524</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4597,10 +4593,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550505</v>
+        <v>550502</v>
       </c>
       <c r="R38" t="n">
-        <v>6994074</v>
+        <v>6993935</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4659,13 +4655,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004541</v>
+        <v>121004537</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4703,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550528</v>
+        <v>550477</v>
       </c>
       <c r="R39" t="n">
-        <v>6994067</v>
+        <v>6994042</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4765,13 +4761,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004547</v>
+        <v>121004540</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4809,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550493</v>
+        <v>550505</v>
       </c>
       <c r="R40" t="n">
-        <v>6994078</v>
+        <v>6994074</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4871,16 +4867,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134246391</v>
+        <v>121004541</v>
       </c>
       <c r="B41" t="n">
-        <v>93271</v>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4906,19 +4902,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550317</v>
+        <v>550528</v>
       </c>
       <c r="R41" t="n">
-        <v>6994117</v>
+        <v>6994067</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4942,12 +4941,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4956,55 +4955,56 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004494</v>
+        <v>121004547</v>
       </c>
       <c r="B42" t="n">
-        <v>93201</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550515</v>
+        <v>550493</v>
       </c>
       <c r="R42" t="n">
-        <v>6993816</v>
+        <v>6994078</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5079,57 +5079,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121004545</v>
+        <v>134246391</v>
       </c>
       <c r="B43" t="n">
-        <v>93201</v>
+        <v>93271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R43" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5153,12 +5150,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,72 +5164,68 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135457522</v>
+        <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93366</v>
+        <v>93400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550478</v>
+        <v>550381</v>
       </c>
       <c r="R44" t="n">
-        <v>6993873</v>
+        <v>6994142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5259,12 +5252,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5273,7 +5266,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5291,16 +5283,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/136617608</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121004409</v>
+        <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93209</v>
+        <v>93400</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5308,40 +5300,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550413</v>
+        <v>550408</v>
       </c>
       <c r="R45" t="n">
-        <v>6994137</v>
+        <v>6994202</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5365,12 +5354,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5379,7 +5368,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5397,16 +5385,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/136618272</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135457649</v>
+        <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>89294</v>
+        <v>93400</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5414,40 +5402,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550447</v>
+        <v>550478</v>
       </c>
       <c r="R46" t="n">
-        <v>6993828</v>
+        <v>6994127</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5471,12 +5456,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,7 +5470,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5503,16 +5487,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457649</t>
+          <t>https://artportalen.se/Sighting/136620831</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102089839</v>
+        <v>121004494</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>93201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,35 +5504,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550410</v>
+        <v>550515</v>
       </c>
       <c r="R47" t="n">
-        <v>6994101</v>
+        <v>6993816</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5575,12 +5561,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5589,6 +5575,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5606,16 +5593,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004337</v>
+        <v>121004545</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>93201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5623,21 +5610,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5650,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550319</v>
+        <v>550493</v>
       </c>
       <c r="R48" t="n">
-        <v>6994143</v>
+        <v>6994078</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5688,11 +5675,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fertil</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5717,16 +5699,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121004358</v>
+        <v>135457522</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>93366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5734,21 +5716,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5761,13 +5743,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550362</v>
+        <v>550478</v>
       </c>
       <c r="R49" t="n">
-        <v>6994156</v>
+        <v>6993873</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5791,12 +5773,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5823,38 +5805,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004395</v>
+        <v>121004409</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5867,10 +5849,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550381</v>
+        <v>550413</v>
       </c>
       <c r="R50" t="n">
-        <v>6994155</v>
+        <v>6994137</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5929,57 +5911,54 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121004439</v>
+        <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>93412</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550405</v>
+        <v>550381</v>
       </c>
       <c r="R51" t="n">
-        <v>6994090</v>
+        <v>6994142</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6003,17 +5982,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6022,7 +5996,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6040,57 +6013,54 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/136617683</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121004450</v>
+        <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>93412</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550379</v>
+        <v>550426</v>
       </c>
       <c r="R52" t="n">
-        <v>6994086</v>
+        <v>6994218</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6114,12 +6084,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6128,7 +6098,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6146,57 +6115,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/136618637</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121004511</v>
+        <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>93412</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550470</v>
+        <v>550392</v>
       </c>
       <c r="R53" t="n">
-        <v>6993852</v>
+        <v>6994015</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6220,17 +6186,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,7 +6200,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6257,57 +6217,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/136621169</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121004515</v>
+        <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>89314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4404</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550464</v>
+        <v>550336</v>
       </c>
       <c r="R54" t="n">
-        <v>6993901</v>
+        <v>6994148</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6331,12 +6288,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6345,7 +6302,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6363,38 +6319,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/136617434</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126099630</v>
+        <v>135457649</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>89294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6403,14 +6359,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550494</v>
+        <v>550447</v>
       </c>
       <c r="R55" t="n">
-        <v>6994148</v>
+        <v>6993828</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6437,17 +6393,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6474,51 +6425,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/135457649</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134246394</v>
+        <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>91622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550512</v>
+        <v>550322</v>
       </c>
       <c r="R56" t="n">
-        <v>6994236</v>
+        <v>6994233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6545,12 +6499,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6559,33 +6513,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/136673687</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134246395</v>
+        <v>102089839</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6611,19 +6566,20 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550292</v>
+        <v>550410</v>
       </c>
       <c r="R57" t="n">
-        <v>6994150</v>
+        <v>6994101</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6647,12 +6603,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6667,63 +6623,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>102089806</v>
+        <v>121004337</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550469</v>
+        <v>550319</v>
       </c>
       <c r="R58" t="n">
-        <v>6994094</v>
+        <v>6994143</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6750,12 +6708,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6764,6 +6727,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6781,38 +6745,38 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004349</v>
+        <v>121004358</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6825,10 +6789,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550358</v>
+        <v>550362</v>
       </c>
       <c r="R59" t="n">
-        <v>6994160</v>
+        <v>6994156</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6887,38 +6851,38 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004374</v>
+        <v>121004395</v>
       </c>
       <c r="B60" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6931,10 +6895,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550369</v>
+        <v>550381</v>
       </c>
       <c r="R60" t="n">
-        <v>6994167</v>
+        <v>6994155</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6993,38 +6957,38 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004533</v>
+        <v>121004439</v>
       </c>
       <c r="B61" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7037,10 +7001,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550456</v>
+        <v>550405</v>
       </c>
       <c r="R61" t="n">
-        <v>6993982</v>
+        <v>6994090</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7077,7 +7041,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På kolad högstubbe</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7104,38 +7068,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126099591</v>
+        <v>121004450</v>
       </c>
       <c r="B62" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7144,14 +7108,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550464</v>
+        <v>550379</v>
       </c>
       <c r="R62" t="n">
-        <v>6994104</v>
+        <v>6994086</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7178,12 +7142,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7210,38 +7174,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126099553</v>
+        <v>121004511</v>
       </c>
       <c r="B63" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7250,14 +7214,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550465</v>
+        <v>550470</v>
       </c>
       <c r="R63" t="n">
-        <v>6994163</v>
+        <v>6993852</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7284,17 +7248,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7321,52 +7285,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>102088995</v>
+        <v>121004515</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550570</v>
+        <v>550464</v>
       </c>
       <c r="R64" t="n">
-        <v>6994156</v>
+        <v>6993901</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7393,17 +7359,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7412,6 +7373,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7429,52 +7391,54 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>102089929</v>
+        <v>126099630</v>
       </c>
       <c r="B65" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550373</v>
+        <v>550494</v>
       </c>
       <c r="R65" t="n">
-        <v>6994082</v>
+        <v>6994148</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7501,12 +7465,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7515,6 +7484,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7532,57 +7502,54 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121004521</v>
+        <v>134246394</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550494</v>
+        <v>550512</v>
       </c>
       <c r="R66" t="n">
-        <v>6993901</v>
+        <v>6994236</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7606,17 +7573,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7625,73 +7587,71 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>102089008</v>
+        <v>134246395</v>
       </c>
       <c r="B67" t="n">
-        <v>80461</v>
+        <v>79373</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550570</v>
+        <v>550292</v>
       </c>
       <c r="R67" t="n">
-        <v>6994156</v>
+        <v>6994150</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7715,17 +7675,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7740,66 +7695,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>102089938</v>
+        <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>80461</v>
+        <v>79474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550373</v>
+        <v>550336</v>
       </c>
       <c r="R68" t="n">
-        <v>6994082</v>
+        <v>6994148</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7823,12 +7777,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7854,38 +7808,38 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/136617444</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102089013</v>
+        <v>102089806</v>
       </c>
       <c r="B69" t="n">
-        <v>80467</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7896,10 +7850,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550570</v>
+        <v>550469</v>
       </c>
       <c r="R69" t="n">
-        <v>6994156</v>
+        <v>6994094</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7934,11 +7888,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7962,52 +7911,54 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>102089935</v>
+        <v>121004349</v>
       </c>
       <c r="B70" t="n">
-        <v>80467</v>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550373</v>
+        <v>550358</v>
       </c>
       <c r="R70" t="n">
-        <v>6994082</v>
+        <v>6994160</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8034,12 +7985,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8048,6 +7999,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8065,59 +8017,54 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121004525</v>
+        <v>121004374</v>
       </c>
       <c r="B71" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550502</v>
+        <v>550369</v>
       </c>
       <c r="R71" t="n">
-        <v>6993935</v>
+        <v>6994167</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8158,6 +8105,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8175,51 +8123,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134246389</v>
+        <v>121004533</v>
       </c>
       <c r="B72" t="n">
-        <v>58131</v>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103023</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550466</v>
+        <v>550456</v>
       </c>
       <c r="R72" t="n">
-        <v>6994147</v>
+        <v>6993982</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8246,12 +8197,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8260,71 +8216,75 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134246392</v>
+        <v>126099591</v>
       </c>
       <c r="B73" t="n">
-        <v>98219</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219815</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550548</v>
+        <v>550464</v>
       </c>
       <c r="R73" t="n">
-        <v>6994192</v>
+        <v>6994104</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8348,12 +8308,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8362,33 +8322,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135466568</v>
+        <v>126099553</v>
       </c>
       <c r="B74" t="n">
-        <v>99328</v>
+        <v>80336</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8396,42 +8357,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550481</v>
+        <v>550465</v>
       </c>
       <c r="R74" t="n">
-        <v>6993999</v>
+        <v>6994163</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8458,12 +8414,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8490,53 +8451,52 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102088784</v>
+        <v>102088995</v>
       </c>
       <c r="B75" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550571</v>
+        <v>550570</v>
       </c>
       <c r="R75" t="n">
-        <v>6994155</v>
+        <v>6994156</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8571,6 +8531,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8594,53 +8559,52 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102089119</v>
+        <v>102089929</v>
       </c>
       <c r="B76" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550567</v>
+        <v>550373</v>
       </c>
       <c r="R76" t="n">
-        <v>6994155</v>
+        <v>6994082</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8698,53 +8662,54 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102089419</v>
+        <v>121004521</v>
       </c>
       <c r="B77" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550554</v>
+        <v>550494</v>
       </c>
       <c r="R77" t="n">
-        <v>6994133</v>
+        <v>6993901</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8771,12 +8736,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8785,6 +8755,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8802,53 +8773,52 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102089819</v>
+        <v>102089008</v>
       </c>
       <c r="B78" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550446</v>
+        <v>550570</v>
       </c>
       <c r="R78" t="n">
-        <v>6994089</v>
+        <v>6994156</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8883,6 +8853,11 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8906,55 +8881,52 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121004332</v>
+        <v>102089938</v>
       </c>
       <c r="B79" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550310</v>
+        <v>550373</v>
       </c>
       <c r="R79" t="n">
-        <v>6994126</v>
+        <v>6994082</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8981,12 +8953,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8995,7 +8967,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9013,55 +8984,52 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121004405</v>
+        <v>102089013</v>
       </c>
       <c r="B80" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550404</v>
+        <v>550570</v>
       </c>
       <c r="R80" t="n">
-        <v>6994153</v>
+        <v>6994156</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9088,12 +9056,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9102,7 +9075,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9120,55 +9092,52 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121004422</v>
+        <v>102089935</v>
       </c>
       <c r="B81" t="n">
-        <v>99118</v>
+        <v>80467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550395</v>
+        <v>550373</v>
       </c>
       <c r="R81" t="n">
-        <v>6994127</v>
+        <v>6994082</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9195,12 +9164,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9209,7 +9178,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9227,55 +9195,59 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004461</v>
+        <v>121004525</v>
       </c>
       <c r="B82" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550389</v>
+        <v>550502</v>
       </c>
       <c r="R82" t="n">
-        <v>6994063</v>
+        <v>6993935</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9316,7 +9288,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9334,58 +9305,62 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121004477</v>
+        <v>136618720</v>
       </c>
       <c r="B83" t="n">
-        <v>99118</v>
+        <v>57193</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550370</v>
+        <v>550460</v>
       </c>
       <c r="R83" t="n">
-        <v>6993853</v>
+        <v>6994253</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9409,12 +9384,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9423,7 +9408,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9441,55 +9425,51 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/136618720</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121004505</v>
+        <v>134246389</v>
       </c>
       <c r="B84" t="n">
-        <v>99118</v>
+        <v>58131</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550496</v>
+        <v>550466</v>
       </c>
       <c r="R84" t="n">
-        <v>6993835</v>
+        <v>6994147</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9516,12 +9496,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9530,76 +9510,71 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121004519</v>
+        <v>134246392</v>
       </c>
       <c r="B85" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550494</v>
+        <v>550548</v>
       </c>
       <c r="R85" t="n">
-        <v>6993901</v>
+        <v>6994192</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9623,17 +9598,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9642,61 +9612,64 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121004558</v>
+        <v>135466568</v>
       </c>
       <c r="B86" t="n">
-        <v>99118</v>
+        <v>99328</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
@@ -9705,10 +9678,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550516</v>
+        <v>550481</v>
       </c>
       <c r="R86" t="n">
-        <v>6994130</v>
+        <v>6993999</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9735,12 +9708,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9767,13 +9740,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121004562</v>
+        <v>102088784</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -9802,20 +9775,18 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550520</v>
+        <v>550571</v>
       </c>
       <c r="R87" t="n">
-        <v>6994154</v>
+        <v>6994155</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9842,12 +9813,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9856,7 +9827,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9874,13 +9844,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121004565</v>
+        <v>102089119</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -9909,20 +9879,18 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550469</v>
+        <v>550567</v>
       </c>
       <c r="R88" t="n">
-        <v>6994270</v>
+        <v>6994155</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9949,12 +9917,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9963,7 +9931,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9981,13 +9948,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126099534</v>
+        <v>102089419</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10016,20 +9983,18 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550463</v>
+        <v>550554</v>
       </c>
       <c r="R89" t="n">
-        <v>6994172</v>
+        <v>6994133</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10056,12 +10021,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10070,7 +10035,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10088,16 +10052,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134246388</v>
+        <v>102089819</v>
       </c>
       <c r="B90" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10123,19 +10087,21 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550414</v>
+        <v>550446</v>
       </c>
       <c r="R90" t="n">
-        <v>6994084</v>
+        <v>6994089</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10159,12 +10125,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10179,27 +10145,27 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135457589</v>
+        <v>121004332</v>
       </c>
       <c r="B91" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10226,11 +10192,7 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
@@ -10239,10 +10201,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550445</v>
+        <v>550310</v>
       </c>
       <c r="R91" t="n">
-        <v>6993808</v>
+        <v>6994126</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10269,17 +10231,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönpyrola.</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10306,16 +10263,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457589</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135457681</v>
+        <v>121004405</v>
       </c>
       <c r="B92" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10342,11 +10299,7 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
@@ -10355,10 +10308,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550350</v>
+        <v>550404</v>
       </c>
       <c r="R92" t="n">
-        <v>6993905</v>
+        <v>6994153</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10385,12 +10338,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10417,16 +10370,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457681</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135457684</v>
+        <v>121004422</v>
       </c>
       <c r="B93" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10453,11 +10406,7 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -10466,10 +10415,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550343</v>
+        <v>550395</v>
       </c>
       <c r="R93" t="n">
-        <v>6993884</v>
+        <v>6994127</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10496,12 +10445,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10528,16 +10477,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457684</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135457690</v>
+        <v>121004461</v>
       </c>
       <c r="B94" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10564,11 +10513,7 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -10577,10 +10522,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550353</v>
+        <v>550389</v>
       </c>
       <c r="R94" t="n">
-        <v>6993851</v>
+        <v>6994063</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10607,12 +10552,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10639,16 +10584,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457690</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135457698</v>
+        <v>121004477</v>
       </c>
       <c r="B95" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10675,11 +10620,7 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -10688,10 +10629,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550455</v>
+        <v>550370</v>
       </c>
       <c r="R95" t="n">
-        <v>6994009</v>
+        <v>6993853</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10718,12 +10659,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10750,47 +10691,43 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457698</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135457602</v>
+        <v>121004505</v>
       </c>
       <c r="B96" t="n">
-        <v>106433</v>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -10799,10 +10736,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550445</v>
+        <v>550496</v>
       </c>
       <c r="R96" t="n">
-        <v>6993808</v>
+        <v>6993835</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10829,17 +10766,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Tillsammans med knärot.</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10866,38 +10798,38 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457602</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135466572</v>
+        <v>121004519</v>
       </c>
       <c r="B97" t="n">
-        <v>98161</v>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10911,10 +10843,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550481</v>
+        <v>550494</v>
       </c>
       <c r="R97" t="n">
-        <v>6993999</v>
+        <v>6993901</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10941,12 +10873,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10973,54 +10910,58 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134246393</v>
+        <v>121004558</v>
       </c>
       <c r="B98" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>550548</v>
+        <v>550516</v>
       </c>
       <c r="R98" t="n">
-        <v>6994192</v>
+        <v>6994130</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11044,12 +10985,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11058,71 +10999,76 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134246406</v>
+        <v>121004562</v>
       </c>
       <c r="B99" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>550277</v>
+        <v>550520</v>
       </c>
       <c r="R99" t="n">
-        <v>6994166</v>
+        <v>6994154</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11146,12 +11092,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11160,71 +11106,73 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126099623</v>
+        <v>121004565</v>
       </c>
       <c r="B100" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>550481</v>
+        <v>550469</v>
       </c>
       <c r="R100" t="n">
-        <v>6994133</v>
+        <v>6994270</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11251,12 +11199,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11283,54 +11231,58 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134246390</v>
+        <v>126099534</v>
       </c>
       <c r="B101" t="n">
-        <v>79131</v>
+        <v>99118</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>550466</v>
+        <v>550463</v>
       </c>
       <c r="R101" t="n">
-        <v>6994147</v>
+        <v>6994172</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11354,12 +11306,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11368,72 +11320,72 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>102089933</v>
+        <v>134246388</v>
       </c>
       <c r="B102" t="n">
-        <v>80392</v>
+        <v>99195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>550373</v>
+        <v>550414</v>
       </c>
       <c r="R102" t="n">
-        <v>6994082</v>
+        <v>6994084</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11457,12 +11409,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11477,18 +11429,1928 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134246388</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>135457589</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457589</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>135457681</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>550350</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6993905</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457681</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>135457684</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>550343</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6993884</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457684</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>135457690</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>550353</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6993851</v>
+      </c>
+      <c r="S106" t="n">
+        <v>25</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457690</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>135457698</v>
+      </c>
+      <c r="B107" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>550455</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6994009</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457698</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>136618852</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>550545</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6994205</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136618852</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>136619024</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>550531</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6994142</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136619024</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>135457602</v>
+      </c>
+      <c r="B110" t="n">
+        <v>106433</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>550445</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6993808</v>
+      </c>
+      <c r="S110" t="n">
+        <v>25</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135457602</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>135466572</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98161</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6993999</v>
+      </c>
+      <c r="S111" t="n">
+        <v>25</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135466572</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>136618893</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98210</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>550520</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6994186</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136618893</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>134246393</v>
+      </c>
+      <c r="B113" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>550548</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6994192</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246393</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S115" t="n">
+        <v>25</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>136617473</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>550358</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6994160</v>
+      </c>
+      <c r="S117" t="n">
+        <v>25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136617473</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>136621098</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>550423</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6994020</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621098</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B119" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/102089933</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>136620458</v>
+      </c>
+      <c r="B120" t="n">
+        <v>93431</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>550496</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6994094</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136620458</t>
         </is>
       </c>
     </row>
@@ -11595,6 +13457,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92675</v>
+        <v>92678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93431</v>
+        <v>93434</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136618720</v>
       </c>
       <c r="B83" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>136617473</v>
       </c>
       <c r="B117" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>136621098</v>
       </c>
       <c r="B118" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93435</v>
+        <v>93440</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92686</v>
+        <v>92688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>136617473</v>
       </c>
       <c r="B117" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>136621098</v>
       </c>
       <c r="B118" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92688</v>
+        <v>92690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>136617473</v>
       </c>
       <c r="B117" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>136621098</v>
       </c>
       <c r="B118" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92690</v>
+        <v>92691</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>136617473</v>
       </c>
       <c r="B117" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>136621098</v>
       </c>
       <c r="B118" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92691</v>
+        <v>92697</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136674026</v>
       </c>
       <c r="B9" t="n">
-        <v>92697</v>
+        <v>92701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136620821</v>
       </c>
       <c r="B19" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>136617608</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>136618272</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>136620831</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>136617683</v>
       </c>
       <c r="B51" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>136618637</v>
       </c>
       <c r="B52" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136621169</v>
       </c>
       <c r="B53" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>136617434</v>
       </c>
       <c r="B54" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>136673687</v>
       </c>
       <c r="B56" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>136617444</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>136618852</v>
       </c>
       <c r="B108" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>136619024</v>
       </c>
       <c r="B109" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>136618893</v>
       </c>
       <c r="B112" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>136617473</v>
       </c>
       <c r="B117" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>136621098</v>
       </c>
       <c r="B118" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>136620458</v>
       </c>
       <c r="B120" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ120"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,32 +1427,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136674026</v>
+        <v>121004536</v>
       </c>
       <c r="B9" t="n">
-        <v>92701</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,17 +1461,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550489</v>
+        <v>550477</v>
       </c>
       <c r="R9" t="n">
-        <v>6993892</v>
+        <v>6994042</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,13 +1527,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136674026</t>
+          <t>https://artportalen.se/Sighting/121004536</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121004536</v>
+        <v>121004550</v>
       </c>
       <c r="B10" t="n">
         <v>81312</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550477</v>
+        <v>550508</v>
       </c>
       <c r="R10" t="n">
-        <v>6994042</v>
+        <v>6994113</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1633,13 +1633,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004536</t>
+          <t>https://artportalen.se/Sighting/121004550</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121004550</v>
+        <v>126099520</v>
       </c>
       <c r="B11" t="n">
         <v>81312</v>
@@ -1673,14 +1673,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550508</v>
+        <v>550419</v>
       </c>
       <c r="R11" t="n">
-        <v>6994113</v>
+        <v>6994207</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,16 +1739,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004550</t>
+          <t>https://artportalen.se/Sighting/126099520</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126099520</v>
+        <v>102089224</v>
       </c>
       <c r="B12" t="n">
-        <v>81312</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,37 +1756,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550419</v>
+        <v>550562</v>
       </c>
       <c r="R12" t="n">
-        <v>6994207</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1813,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,52 +1842,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099520</t>
+          <t>https://artportalen.se/Sighting/102089224</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102089224</v>
+        <v>121004416</v>
       </c>
       <c r="B13" t="n">
-        <v>83173</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550562</v>
+        <v>550398</v>
       </c>
       <c r="R13" t="n">
-        <v>6994152</v>
+        <v>6994131</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1917,12 +1916,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,6 +1930,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1948,13 +1948,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089224</t>
+          <t>https://artportalen.se/Sighting/121004416</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121004416</v>
+        <v>121004472</v>
       </c>
       <c r="B14" t="n">
         <v>92083</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550398</v>
+        <v>550400</v>
       </c>
       <c r="R14" t="n">
-        <v>6994131</v>
+        <v>6993983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,38 +2054,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004416</t>
+          <t>https://artportalen.se/Sighting/121004472</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121004472</v>
+        <v>121004362</v>
       </c>
       <c r="B15" t="n">
-        <v>92083</v>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550400</v>
+        <v>550364</v>
       </c>
       <c r="R15" t="n">
-        <v>6993983</v>
+        <v>6994169</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004472</t>
+          <t>https://artportalen.se/Sighting/121004362</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004362</v>
+        <v>121004490</v>
       </c>
       <c r="B16" t="n">
         <v>90932</v>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550364</v>
+        <v>550508</v>
       </c>
       <c r="R16" t="n">
-        <v>6994169</v>
+        <v>6993803</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,13 +2266,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004362</t>
+          <t>https://artportalen.se/Sighting/121004490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121004490</v>
+        <v>121004539</v>
       </c>
       <c r="B17" t="n">
         <v>90932</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550508</v>
+        <v>550486</v>
       </c>
       <c r="R17" t="n">
-        <v>6993803</v>
+        <v>6994062</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2372,16 +2372,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004490</t>
+          <t>https://artportalen.se/Sighting/121004539</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121004539</v>
+        <v>136620821</v>
       </c>
       <c r="B18" t="n">
-        <v>90932</v>
+        <v>91132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,22 +2407,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550486</v>
+        <v>550478</v>
       </c>
       <c r="R18" t="n">
-        <v>6994062</v>
+        <v>6994127</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,12 +2443,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2460,7 +2457,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2478,16 +2474,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004539</t>
+          <t>https://artportalen.se/Sighting/136620821</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136620821</v>
+        <v>62025591</v>
       </c>
       <c r="B19" t="n">
-        <v>91132</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,34 +2491,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550478</v>
+        <v>550409</v>
       </c>
       <c r="R19" t="n">
-        <v>6994127</v>
+        <v>6994048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,12 +2545,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2565,31 +2561,41 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Mjuk tallåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136620821</t>
+          <t>https://artportalen.se/Sighting/62025591</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>62025591</v>
+        <v>102089002</v>
       </c>
       <c r="B20" t="n">
-        <v>91962</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,37 +2603,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550409</v>
+        <v>550570</v>
       </c>
       <c r="R20" t="n">
-        <v>6994048</v>
+        <v>6994156</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2651,12 +2658,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2667,80 +2679,69 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Mjuk tallåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025591</t>
+          <t>https://artportalen.se/Sighting/102089002</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102089002</v>
+        <v>103996059</v>
       </c>
       <c r="B21" t="n">
-        <v>80433</v>
+        <v>96338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550570</v>
+        <v>550310</v>
       </c>
       <c r="R21" t="n">
-        <v>6994156</v>
+        <v>6994183</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2764,17 +2765,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,6 +2791,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2794,60 +2805,67 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089002</t>
+          <t>https://artportalen.se/Sighting/103996059</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103996059</v>
+        <v>121004351</v>
       </c>
       <c r="B22" t="n">
-        <v>96338</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550310</v>
+        <v>550358</v>
       </c>
       <c r="R22" t="n">
-        <v>6994183</v>
+        <v>6994160</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2871,22 +2889,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:43</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,13 +2903,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2911,23 +2915,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996059</t>
+          <t>https://artportalen.se/Sighting/121004351</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004351</v>
+        <v>121004470</v>
       </c>
       <c r="B23" t="n">
         <v>91831</v>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550358</v>
+        <v>550383</v>
       </c>
       <c r="R23" t="n">
-        <v>6994160</v>
+        <v>6993994</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3003,6 +3003,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3027,16 +3032,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004351</t>
+          <t>https://artportalen.se/Sighting/121004470</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004470</v>
+        <v>135457707</v>
       </c>
       <c r="B24" t="n">
-        <v>91831</v>
+        <v>93354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3242</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550383</v>
+        <v>550510</v>
       </c>
       <c r="R24" t="n">
-        <v>6993994</v>
+        <v>6993821</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3101,17 +3106,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3138,16 +3138,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004470</t>
+          <t>https://artportalen.se/Sighting/135457707</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135457707</v>
+        <v>62025592</v>
       </c>
       <c r="B25" t="n">
-        <v>93354</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,40 +3155,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Hoberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550510</v>
+        <v>550409</v>
       </c>
       <c r="R25" t="n">
-        <v>6993821</v>
+        <v>6994048</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3212,12 +3209,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2016-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,31 +3223,40 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Torr, mossig mark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457707</t>
+          <t>https://artportalen.se/Sighting/62025592</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>62025592</v>
+        <v>102089700</v>
       </c>
       <c r="B26" t="n">
         <v>93197</v>
@@ -3279,19 +3285,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hoberget, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550409</v>
+        <v>550476</v>
       </c>
       <c r="R26" t="n">
-        <v>6994048</v>
+        <v>6994117</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3315,12 +3322,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3331,38 +3338,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Torr, mossig mark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62025592</t>
+          <t>https://artportalen.se/Sighting/102089700</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102089700</v>
+        <v>103996072</v>
       </c>
       <c r="B27" t="n">
         <v>93197</v>
@@ -3391,20 +3388,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550476</v>
+        <v>550481</v>
       </c>
       <c r="R27" t="n">
-        <v>6994117</v>
+        <v>6994068</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3428,12 +3424,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,6 +3450,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3453,19 +3464,23 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089700</t>
+          <t>https://artportalen.se/Sighting/103996072</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103996072</v>
+        <v>103996080</v>
       </c>
       <c r="B28" t="n">
         <v>93197</v>
@@ -3500,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550481</v>
+        <v>550485</v>
       </c>
       <c r="R28" t="n">
-        <v>6994068</v>
+        <v>6994105</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3545,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3580,13 +3595,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996072</t>
+          <t>https://artportalen.se/Sighting/103996080</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103996080</v>
+        <v>121004341</v>
       </c>
       <c r="B29" t="n">
         <v>93197</v>
@@ -3615,19 +3630,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550485</v>
+        <v>550344</v>
       </c>
       <c r="R29" t="n">
-        <v>6994105</v>
+        <v>6994160</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3651,22 +3669,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,13 +3683,9 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3691,23 +3695,19 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103996080</t>
+          <t>https://artportalen.se/Sighting/121004341</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121004341</v>
+        <v>121004394</v>
       </c>
       <c r="B30" t="n">
         <v>93197</v>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550344</v>
+        <v>550381</v>
       </c>
       <c r="R30" t="n">
-        <v>6994160</v>
+        <v>6994155</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3807,13 +3807,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004341</t>
+          <t>https://artportalen.se/Sighting/121004394</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121004394</v>
+        <v>121004399</v>
       </c>
       <c r="B31" t="n">
         <v>93197</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550381</v>
+        <v>550384</v>
       </c>
       <c r="R31" t="n">
-        <v>6994155</v>
+        <v>6994151</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3913,13 +3913,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004394</t>
+          <t>https://artportalen.se/Sighting/121004399</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121004399</v>
+        <v>121004430</v>
       </c>
       <c r="B32" t="n">
         <v>93197</v>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550384</v>
+        <v>550422</v>
       </c>
       <c r="R32" t="n">
-        <v>6994151</v>
+        <v>6994093</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4019,13 +4019,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004399</t>
+          <t>https://artportalen.se/Sighting/121004430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121004430</v>
+        <v>121004475</v>
       </c>
       <c r="B33" t="n">
         <v>93197</v>
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550422</v>
+        <v>550385</v>
       </c>
       <c r="R33" t="n">
-        <v>6994093</v>
+        <v>6993920</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4125,13 +4125,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004430</t>
+          <t>https://artportalen.se/Sighting/121004475</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121004475</v>
+        <v>121004484</v>
       </c>
       <c r="B34" t="n">
         <v>93197</v>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550385</v>
+        <v>550427</v>
       </c>
       <c r="R34" t="n">
-        <v>6993920</v>
+        <v>6993867</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4231,13 +4231,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004475</t>
+          <t>https://artportalen.se/Sighting/121004484</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121004484</v>
+        <v>121004500</v>
       </c>
       <c r="B35" t="n">
         <v>93197</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550427</v>
+        <v>550496</v>
       </c>
       <c r="R35" t="n">
-        <v>6993867</v>
+        <v>6993817</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4337,13 +4337,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004484</t>
+          <t>https://artportalen.se/Sighting/121004500</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121004500</v>
+        <v>121004509</v>
       </c>
       <c r="B36" t="n">
         <v>93197</v>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550496</v>
+        <v>550476</v>
       </c>
       <c r="R36" t="n">
-        <v>6993817</v>
+        <v>6993841</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4443,13 +4443,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004500</t>
+          <t>https://artportalen.se/Sighting/121004509</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121004509</v>
+        <v>121004524</v>
       </c>
       <c r="B37" t="n">
         <v>93197</v>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550476</v>
+        <v>550502</v>
       </c>
       <c r="R37" t="n">
-        <v>6993841</v>
+        <v>6993935</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4549,13 +4549,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004509</t>
+          <t>https://artportalen.se/Sighting/121004524</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121004524</v>
+        <v>121004537</v>
       </c>
       <c r="B38" t="n">
         <v>93197</v>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550502</v>
+        <v>550477</v>
       </c>
       <c r="R38" t="n">
-        <v>6993935</v>
+        <v>6994042</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4655,13 +4655,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004524</t>
+          <t>https://artportalen.se/Sighting/121004537</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121004537</v>
+        <v>121004540</v>
       </c>
       <c r="B39" t="n">
         <v>93197</v>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550477</v>
+        <v>550505</v>
       </c>
       <c r="R39" t="n">
-        <v>6994042</v>
+        <v>6994074</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4761,13 +4761,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004537</t>
+          <t>https://artportalen.se/Sighting/121004540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121004540</v>
+        <v>121004541</v>
       </c>
       <c r="B40" t="n">
         <v>93197</v>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550505</v>
+        <v>550528</v>
       </c>
       <c r="R40" t="n">
-        <v>6994074</v>
+        <v>6994067</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4867,13 +4867,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004540</t>
+          <t>https://artportalen.se/Sighting/121004541</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121004541</v>
+        <v>121004547</v>
       </c>
       <c r="B41" t="n">
         <v>93197</v>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550528</v>
+        <v>550493</v>
       </c>
       <c r="R41" t="n">
-        <v>6994067</v>
+        <v>6994078</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4973,16 +4973,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004541</t>
+          <t>https://artportalen.se/Sighting/121004547</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121004547</v>
+        <v>134246391</v>
       </c>
       <c r="B42" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5008,22 +5008,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550493</v>
+        <v>550317</v>
       </c>
       <c r="R42" t="n">
-        <v>6994078</v>
+        <v>6994117</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5047,12 +5044,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5061,34 +5058,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004547</t>
+          <t>https://artportalen.se/Sighting/134246391</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134246391</v>
+        <v>136617608</v>
       </c>
       <c r="B43" t="n">
-        <v>93271</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5116,14 +5112,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550317</v>
+        <v>550381</v>
       </c>
       <c r="R43" t="n">
-        <v>6994117</v>
+        <v>6994142</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,12 +5146,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5170,24 +5166,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246391</t>
+          <t>https://artportalen.se/Sighting/136617608</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136617608</v>
+        <v>136618272</v>
       </c>
       <c r="B44" t="n">
         <v>93426</v>
@@ -5222,10 +5218,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550381</v>
+        <v>550408</v>
       </c>
       <c r="R44" t="n">
-        <v>6994142</v>
+        <v>6994202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5283,13 +5279,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136617608</t>
+          <t>https://artportalen.se/Sighting/136618272</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136618272</v>
+        <v>136620831</v>
       </c>
       <c r="B45" t="n">
         <v>93426</v>
@@ -5320,14 +5316,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550408</v>
+        <v>550478</v>
       </c>
       <c r="R45" t="n">
-        <v>6994202</v>
+        <v>6994127</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5385,13 +5381,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136618272</t>
+          <t>https://artportalen.se/Sighting/136620831</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136620831</v>
+        <v>137201461</v>
       </c>
       <c r="B46" t="n">
         <v>93426</v>
@@ -5420,16 +5416,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550478</v>
+        <v>550457</v>
       </c>
       <c r="R46" t="n">
-        <v>6994127</v>
+        <v>6993847</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5470,6 +5469,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5487,38 +5487,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136620831</t>
+          <t>https://artportalen.se/Sighting/137201461</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121004494</v>
+        <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93201</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5531,13 +5531,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550515</v>
+        <v>550442</v>
       </c>
       <c r="R47" t="n">
-        <v>6993816</v>
+        <v>6993869</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5561,12 +5561,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,13 +5593,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004494</t>
+          <t>https://artportalen.se/Sighting/137201516</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121004545</v>
+        <v>121004494</v>
       </c>
       <c r="B48" t="n">
         <v>93201</v>
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550493</v>
+        <v>550515</v>
       </c>
       <c r="R48" t="n">
-        <v>6994078</v>
+        <v>6993816</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5699,16 +5699,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004545</t>
+          <t>https://artportalen.se/Sighting/121004494</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135457522</v>
+        <v>121004545</v>
       </c>
       <c r="B49" t="n">
-        <v>93366</v>
+        <v>93201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550478</v>
+        <v>550493</v>
       </c>
       <c r="R49" t="n">
-        <v>6993873</v>
+        <v>6994078</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5773,12 +5773,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5805,38 +5805,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457522</t>
+          <t>https://artportalen.se/Sighting/121004545</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121004409</v>
+        <v>135457522</v>
       </c>
       <c r="B50" t="n">
-        <v>93209</v>
+        <v>93366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550413</v>
+        <v>550478</v>
       </c>
       <c r="R50" t="n">
-        <v>6994137</v>
+        <v>6993873</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5879,12 +5879,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5911,16 +5911,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004409</t>
+          <t>https://artportalen.se/Sighting/135457522</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136617683</v>
+        <v>121004409</v>
       </c>
       <c r="B51" t="n">
-        <v>93438</v>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5946,19 +5946,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550381</v>
+        <v>550413</v>
       </c>
       <c r="R51" t="n">
-        <v>6994142</v>
+        <v>6994137</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5982,12 +5985,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5996,6 +5999,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6013,13 +6017,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136617683</t>
+          <t>https://artportalen.se/Sighting/121004409</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136618637</v>
+        <v>136617683</v>
       </c>
       <c r="B52" t="n">
         <v>93438</v>
@@ -6054,10 +6058,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550426</v>
+        <v>550381</v>
       </c>
       <c r="R52" t="n">
-        <v>6994218</v>
+        <v>6994142</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6115,13 +6119,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136618637</t>
+          <t>https://artportalen.se/Sighting/136617683</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136621169</v>
+        <v>136618637</v>
       </c>
       <c r="B53" t="n">
         <v>93438</v>
@@ -6156,10 +6160,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550392</v>
+        <v>550426</v>
       </c>
       <c r="R53" t="n">
-        <v>6994015</v>
+        <v>6994218</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6217,16 +6221,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621169</t>
+          <t>https://artportalen.se/Sighting/136618637</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136617434</v>
+        <v>136621169</v>
       </c>
       <c r="B54" t="n">
-        <v>89335</v>
+        <v>93438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6234,21 +6238,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4404</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sotvaxskivling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus camarophyllus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6258,10 +6262,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550336</v>
+        <v>550392</v>
       </c>
       <c r="R54" t="n">
-        <v>6994148</v>
+        <v>6994015</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6319,16 +6323,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136617434</t>
+          <t>https://artportalen.se/Sighting/136621169</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135457649</v>
+        <v>136617434</v>
       </c>
       <c r="B55" t="n">
-        <v>89294</v>
+        <v>89335</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6336,40 +6340,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4412</v>
+        <v>4404</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550447</v>
+        <v>550336</v>
       </c>
       <c r="R55" t="n">
-        <v>6993828</v>
+        <v>6994148</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6393,12 +6394,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6407,7 +6408,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6425,16 +6425,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457649</t>
+          <t>https://artportalen.se/Sighting/136617434</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136673687</v>
+        <v>135457649</v>
       </c>
       <c r="B56" t="n">
-        <v>91643</v>
+        <v>89294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6442,21 +6442,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5754</v>
+        <v>4412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6465,17 +6465,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skog vid Lappbrännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550322</v>
+        <v>550447</v>
       </c>
       <c r="R56" t="n">
-        <v>6994233</v>
+        <v>6993828</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6499,12 +6499,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6531,55 +6531,57 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136673687</t>
+          <t>https://artportalen.se/Sighting/135457649</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>102089839</v>
+        <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>89353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550410</v>
+        <v>550505</v>
       </c>
       <c r="R57" t="n">
-        <v>6994101</v>
+        <v>6994089</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6603,12 +6605,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6617,6 +6619,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6634,38 +6637,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089839</t>
+          <t>https://artportalen.se/Sighting/137202122</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121004337</v>
+        <v>136673687</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>91643</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6674,17 +6677,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Lappbrännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550319</v>
+        <v>550322</v>
       </c>
       <c r="R58" t="n">
-        <v>6994143</v>
+        <v>6994233</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6708,17 +6711,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6745,13 +6743,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004337</t>
+          <t>https://artportalen.se/Sighting/136673687</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121004358</v>
+        <v>102089839</v>
       </c>
       <c r="B59" t="n">
         <v>79327</v>
@@ -6780,19 +6778,17 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550362</v>
+        <v>550410</v>
       </c>
       <c r="R59" t="n">
-        <v>6994156</v>
+        <v>6994101</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6819,12 +6815,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6833,7 +6829,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6851,13 +6846,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004358</t>
+          <t>https://artportalen.se/Sighting/102089839</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121004395</v>
+        <v>121004337</v>
       </c>
       <c r="B60" t="n">
         <v>79327</v>
@@ -6895,10 +6890,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550381</v>
+        <v>550319</v>
       </c>
       <c r="R60" t="n">
-        <v>6994155</v>
+        <v>6994143</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6933,6 +6928,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Fertil</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6957,13 +6957,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004395</t>
+          <t>https://artportalen.se/Sighting/121004337</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121004439</v>
+        <v>121004358</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -7001,10 +7001,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550405</v>
+        <v>550362</v>
       </c>
       <c r="R61" t="n">
-        <v>6994090</v>
+        <v>6994156</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7039,11 +7039,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7068,13 +7063,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004439</t>
+          <t>https://artportalen.se/Sighting/121004358</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121004450</v>
+        <v>121004395</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7112,10 +7107,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550379</v>
+        <v>550381</v>
       </c>
       <c r="R62" t="n">
-        <v>6994086</v>
+        <v>6994155</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7174,13 +7169,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004450</t>
+          <t>https://artportalen.se/Sighting/121004395</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121004511</v>
+        <v>121004439</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7218,10 +7213,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550470</v>
+        <v>550405</v>
       </c>
       <c r="R63" t="n">
-        <v>6993852</v>
+        <v>6994090</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7285,13 +7280,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004511</t>
+          <t>https://artportalen.se/Sighting/121004439</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121004515</v>
+        <v>121004450</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7329,10 +7324,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550464</v>
+        <v>550379</v>
       </c>
       <c r="R64" t="n">
-        <v>6993901</v>
+        <v>6994086</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7391,13 +7386,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004515</t>
+          <t>https://artportalen.se/Sighting/121004450</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126099630</v>
+        <v>121004511</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7431,14 +7426,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550494</v>
+        <v>550470</v>
       </c>
       <c r="R65" t="n">
-        <v>6994148</v>
+        <v>6993852</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7465,12 +7460,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7502,16 +7497,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099630</t>
+          <t>https://artportalen.se/Sighting/121004511</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134246394</v>
+        <v>121004515</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7537,19 +7532,22 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550512</v>
+        <v>550464</v>
       </c>
       <c r="R66" t="n">
-        <v>6994236</v>
+        <v>6993901</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7573,12 +7571,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7587,33 +7585,34 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246394</t>
+          <t>https://artportalen.se/Sighting/121004515</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134246395</v>
+        <v>126099630</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7639,19 +7638,22 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550292</v>
+        <v>550494</v>
       </c>
       <c r="R67" t="n">
-        <v>6994150</v>
+        <v>6994148</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7675,12 +7677,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7689,33 +7696,34 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246395</t>
+          <t>https://artportalen.se/Sighting/126099630</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136617444</v>
+        <v>134246394</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7743,14 +7751,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550336</v>
+        <v>550512</v>
       </c>
       <c r="R68" t="n">
-        <v>6994148</v>
+        <v>6994236</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7777,12 +7785,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7797,66 +7805,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136617444</t>
+          <t>https://artportalen.se/Sighting/134246394</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>102089806</v>
+        <v>134246395</v>
       </c>
       <c r="B69" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550469</v>
+        <v>550292</v>
       </c>
       <c r="R69" t="n">
-        <v>6994094</v>
+        <v>6994150</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7880,12 +7887,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7900,68 +7907,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089806</t>
+          <t>https://artportalen.se/Sighting/134246395</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121004349</v>
+        <v>136617444</v>
       </c>
       <c r="B70" t="n">
-        <v>79946</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550358</v>
+        <v>550336</v>
       </c>
       <c r="R70" t="n">
-        <v>6994160</v>
+        <v>6994148</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7985,12 +7989,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7999,7 +8003,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8017,13 +8020,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004349</t>
+          <t>https://artportalen.se/Sighting/136617444</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121004374</v>
+        <v>102089806</v>
       </c>
       <c r="B71" t="n">
         <v>79946</v>
@@ -8052,19 +8055,17 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550369</v>
+        <v>550469</v>
       </c>
       <c r="R71" t="n">
-        <v>6994167</v>
+        <v>6994094</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8091,12 +8092,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8105,7 +8106,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8123,13 +8123,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004374</t>
+          <t>https://artportalen.se/Sighting/102089806</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121004533</v>
+        <v>121004349</v>
       </c>
       <c r="B72" t="n">
         <v>79946</v>
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550456</v>
+        <v>550358</v>
       </c>
       <c r="R72" t="n">
-        <v>6993982</v>
+        <v>6994160</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8205,11 +8205,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8234,13 +8229,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004533</t>
+          <t>https://artportalen.se/Sighting/121004349</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126099591</v>
+        <v>121004374</v>
       </c>
       <c r="B73" t="n">
         <v>79946</v>
@@ -8274,14 +8269,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550464</v>
+        <v>550369</v>
       </c>
       <c r="R73" t="n">
-        <v>6994104</v>
+        <v>6994167</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8308,12 +8303,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8340,38 +8335,38 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099591</t>
+          <t>https://artportalen.se/Sighting/121004374</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126099553</v>
+        <v>121004533</v>
       </c>
       <c r="B74" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8380,14 +8375,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550465</v>
+        <v>550456</v>
       </c>
       <c r="R74" t="n">
-        <v>6994163</v>
+        <v>6993982</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8414,17 +8409,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På kolad högstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8451,16 +8446,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099553</t>
+          <t>https://artportalen.se/Sighting/121004533</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102088995</v>
+        <v>126099591</v>
       </c>
       <c r="B75" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8468,35 +8463,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550570</v>
+        <v>550464</v>
       </c>
       <c r="R75" t="n">
-        <v>6994156</v>
+        <v>6994104</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8523,17 +8520,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8542,6 +8534,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8559,52 +8552,54 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088995</t>
+          <t>https://artportalen.se/Sighting/126099591</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102089929</v>
+        <v>126099553</v>
       </c>
       <c r="B76" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550373</v>
+        <v>550465</v>
       </c>
       <c r="R76" t="n">
-        <v>6994082</v>
+        <v>6994163</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8631,12 +8626,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8645,6 +8645,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8662,13 +8663,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089929</t>
+          <t>https://artportalen.se/Sighting/126099553</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121004521</v>
+        <v>102088995</v>
       </c>
       <c r="B77" t="n">
         <v>80432</v>
@@ -8697,19 +8698,17 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550494</v>
+        <v>550570</v>
       </c>
       <c r="R77" t="n">
-        <v>6993901</v>
+        <v>6994156</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8736,12 +8735,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -8755,7 +8754,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8773,38 +8771,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004521</t>
+          <t>https://artportalen.se/Sighting/102088995</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102089008</v>
+        <v>102089929</v>
       </c>
       <c r="B78" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8815,10 +8813,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550570</v>
+        <v>550373</v>
       </c>
       <c r="R78" t="n">
-        <v>6994156</v>
+        <v>6994082</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8853,11 +8851,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8881,52 +8874,54 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089008</t>
+          <t>https://artportalen.se/Sighting/102089929</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102089938</v>
+        <v>121004521</v>
       </c>
       <c r="B79" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550373</v>
+        <v>550494</v>
       </c>
       <c r="R79" t="n">
-        <v>6994082</v>
+        <v>6993901</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8953,12 +8948,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8967,6 +8967,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8984,16 +8985,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089938</t>
+          <t>https://artportalen.se/Sighting/121004521</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>102089013</v>
+        <v>102089008</v>
       </c>
       <c r="B80" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9001,21 +9002,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9092,16 +9093,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089013</t>
+          <t>https://artportalen.se/Sighting/102089008</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>102089935</v>
+        <v>102089938</v>
       </c>
       <c r="B81" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9109,21 +9110,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9195,16 +9196,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089935</t>
+          <t>https://artportalen.se/Sighting/102089938</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121004525</v>
+        <v>102089013</v>
       </c>
       <c r="B82" t="n">
-        <v>57141</v>
+        <v>80467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9212,42 +9213,35 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550502</v>
+        <v>550570</v>
       </c>
       <c r="R82" t="n">
-        <v>6993935</v>
+        <v>6994156</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9274,12 +9268,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9305,16 +9304,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004525</t>
+          <t>https://artportalen.se/Sighting/102089013</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136618720</v>
+        <v>102089935</v>
       </c>
       <c r="B83" t="n">
-        <v>57195</v>
+        <v>80467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,45 +9321,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550460</v>
+        <v>550373</v>
       </c>
       <c r="R83" t="n">
-        <v>6994253</v>
+        <v>6994082</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,22 +9376,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9425,16 +9407,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136618720</t>
+          <t>https://artportalen.se/Sighting/102089935</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134246389</v>
+        <v>121004525</v>
       </c>
       <c r="B84" t="n">
-        <v>58131</v>
+        <v>57141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9442,34 +9424,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103023</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550466</v>
+        <v>550502</v>
       </c>
       <c r="R84" t="n">
-        <v>6994147</v>
+        <v>6993935</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9496,12 +9486,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9516,27 +9506,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246389</t>
+          <t>https://artportalen.se/Sighting/121004525</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134246392</v>
+        <v>136618720</v>
       </c>
       <c r="B85" t="n">
-        <v>98219</v>
+        <v>57195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9544,37 +9534,45 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219815</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550548</v>
+        <v>550460</v>
       </c>
       <c r="R85" t="n">
-        <v>6994192</v>
+        <v>6994253</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9598,12 +9596,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9618,27 +9626,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246392</t>
+          <t>https://artportalen.se/Sighting/136618720</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135466568</v>
+        <v>134246389</v>
       </c>
       <c r="B86" t="n">
-        <v>99328</v>
+        <v>58131</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9646,42 +9654,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219874</v>
+        <v>103023</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550481</v>
+        <v>550466</v>
       </c>
       <c r="R86" t="n">
-        <v>6993999</v>
+        <v>6994147</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9708,12 +9708,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9722,74 +9722,71 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466568</t>
+          <t>https://artportalen.se/Sighting/134246389</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>102088784</v>
+        <v>134246392</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>98219</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550571</v>
+        <v>550548</v>
       </c>
       <c r="R87" t="n">
-        <v>6994155</v>
+        <v>6994192</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9813,12 +9810,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9833,64 +9830,70 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102088784</t>
+          <t>https://artportalen.se/Sighting/134246392</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>102089119</v>
+        <v>135466568</v>
       </c>
       <c r="B88" t="n">
-        <v>99118</v>
+        <v>99328</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550567</v>
+        <v>550481</v>
       </c>
       <c r="R88" t="n">
-        <v>6994155</v>
+        <v>6993999</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9917,12 +9920,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9931,6 +9934,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9948,56 +9952,58 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089119</t>
+          <t>https://artportalen.se/Sighting/135466568</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>102089419</v>
+        <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>99409</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>550554</v>
+        <v>550479</v>
       </c>
       <c r="R89" t="n">
-        <v>6994133</v>
+        <v>6993998</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10021,12 +10027,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10035,6 +10041,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10052,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089419</t>
+          <t>https://artportalen.se/Sighting/137201958</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102089819</v>
+        <v>102088784</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -10091,14 +10098,14 @@
       <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>550446</v>
+        <v>550571</v>
       </c>
       <c r="R90" t="n">
-        <v>6994089</v>
+        <v>6994155</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10156,13 +10163,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089819</t>
+          <t>https://artportalen.se/Sighting/102088784</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121004332</v>
+        <v>102089119</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -10191,20 +10198,18 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>550310</v>
+        <v>550567</v>
       </c>
       <c r="R91" t="n">
-        <v>6994126</v>
+        <v>6994155</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10231,12 +10236,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10245,7 +10250,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10263,13 +10267,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004332</t>
+          <t>https://artportalen.se/Sighting/102089119</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121004405</v>
+        <v>102089419</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -10298,20 +10302,18 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>550404</v>
+        <v>550554</v>
       </c>
       <c r="R92" t="n">
-        <v>6994153</v>
+        <v>6994133</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10338,12 +10340,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10352,7 +10354,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10370,13 +10371,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004405</t>
+          <t>https://artportalen.se/Sighting/102089419</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121004422</v>
+        <v>102089819</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -10405,20 +10406,18 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>550395</v>
+        <v>550446</v>
       </c>
       <c r="R93" t="n">
-        <v>6994127</v>
+        <v>6994089</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10445,12 +10444,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10459,7 +10458,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10477,13 +10475,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004422</t>
+          <t>https://artportalen.se/Sighting/102089819</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121004461</v>
+        <v>121004332</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -10522,10 +10520,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>550389</v>
+        <v>550310</v>
       </c>
       <c r="R94" t="n">
-        <v>6994063</v>
+        <v>6994126</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10584,13 +10582,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004461</t>
+          <t>https://artportalen.se/Sighting/121004332</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121004477</v>
+        <v>121004405</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -10629,10 +10627,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>550370</v>
+        <v>550404</v>
       </c>
       <c r="R95" t="n">
-        <v>6993853</v>
+        <v>6994153</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10691,13 +10689,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004477</t>
+          <t>https://artportalen.se/Sighting/121004405</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121004505</v>
+        <v>121004422</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -10736,10 +10734,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>550496</v>
+        <v>550395</v>
       </c>
       <c r="R96" t="n">
-        <v>6993835</v>
+        <v>6994127</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10798,13 +10796,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004505</t>
+          <t>https://artportalen.se/Sighting/121004422</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121004519</v>
+        <v>121004461</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -10843,10 +10841,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>550494</v>
+        <v>550389</v>
       </c>
       <c r="R97" t="n">
-        <v>6993901</v>
+        <v>6994063</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10881,11 +10879,6 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Vid sälg som är draperad i lunglav.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10910,13 +10903,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004519</t>
+          <t>https://artportalen.se/Sighting/121004461</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121004558</v>
+        <v>121004477</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -10955,10 +10948,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>550516</v>
+        <v>550370</v>
       </c>
       <c r="R98" t="n">
-        <v>6994130</v>
+        <v>6993853</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11017,13 +11010,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004558</t>
+          <t>https://artportalen.se/Sighting/121004477</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121004562</v>
+        <v>121004505</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -11062,10 +11055,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>550520</v>
+        <v>550496</v>
       </c>
       <c r="R99" t="n">
-        <v>6994154</v>
+        <v>6993835</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11124,13 +11117,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004562</t>
+          <t>https://artportalen.se/Sighting/121004505</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121004565</v>
+        <v>121004519</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -11169,10 +11162,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>550469</v>
+        <v>550494</v>
       </c>
       <c r="R100" t="n">
-        <v>6994270</v>
+        <v>6993901</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11207,6 +11200,11 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Vid sälg som är draperad i lunglav.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11231,13 +11229,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121004565</t>
+          <t>https://artportalen.se/Sighting/121004519</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126099534</v>
+        <v>121004558</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -11272,14 +11270,14 @@
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>550463</v>
+        <v>550516</v>
       </c>
       <c r="R101" t="n">
-        <v>6994172</v>
+        <v>6994130</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11306,12 +11304,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11338,16 +11336,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099534</t>
+          <t>https://artportalen.se/Sighting/121004558</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134246388</v>
+        <v>121004562</v>
       </c>
       <c r="B102" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11373,19 +11371,23 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>550414</v>
+        <v>550520</v>
       </c>
       <c r="R102" t="n">
-        <v>6994084</v>
+        <v>6994154</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11409,12 +11411,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11423,33 +11425,34 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246388</t>
+          <t>https://artportalen.se/Sighting/121004562</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135457589</v>
+        <v>121004565</v>
       </c>
       <c r="B103" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11476,11 +11479,7 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -11489,10 +11488,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>550445</v>
+        <v>550469</v>
       </c>
       <c r="R103" t="n">
-        <v>6993808</v>
+        <v>6994270</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11519,17 +11518,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Tillsammans med grönpyrola.</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11556,16 +11550,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457589</t>
+          <t>https://artportalen.se/Sighting/121004565</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135457681</v>
+        <v>126099534</v>
       </c>
       <c r="B104" t="n">
-        <v>99293</v>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11592,23 +11586,19 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>550350</v>
+        <v>550463</v>
       </c>
       <c r="R104" t="n">
-        <v>6993905</v>
+        <v>6994172</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11635,12 +11625,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11667,16 +11657,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457681</t>
+          <t>https://artportalen.se/Sighting/126099534</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135457684</v>
+        <v>134246388</v>
       </c>
       <c r="B105" t="n">
-        <v>99293</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11702,27 +11692,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>550343</v>
+        <v>550414</v>
       </c>
       <c r="R105" t="n">
-        <v>6993884</v>
+        <v>6994084</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11746,12 +11728,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11760,31 +11742,30 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457684</t>
+          <t>https://artportalen.se/Sighting/134246388</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135457690</v>
+        <v>135457589</v>
       </c>
       <c r="B106" t="n">
         <v>99293</v>
@@ -11827,10 +11808,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>550353</v>
+        <v>550445</v>
       </c>
       <c r="R106" t="n">
-        <v>6993851</v>
+        <v>6993808</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11865,6 +11846,11 @@
           <t>2026-07-27</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Tillsammans med grönpyrola.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11889,13 +11875,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457690</t>
+          <t>https://artportalen.se/Sighting/135457589</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135457698</v>
+        <v>135457681</v>
       </c>
       <c r="B107" t="n">
         <v>99293</v>
@@ -11938,10 +11924,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>550455</v>
+        <v>550350</v>
       </c>
       <c r="R107" t="n">
-        <v>6994009</v>
+        <v>6993905</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12000,16 +11986,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457698</t>
+          <t>https://artportalen.se/Sighting/135457681</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136618852</v>
+        <v>135457684</v>
       </c>
       <c r="B108" t="n">
-        <v>99372</v>
+        <v>99293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12035,19 +12021,27 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>550545</v>
+        <v>550343</v>
       </c>
       <c r="R108" t="n">
-        <v>6994205</v>
+        <v>6993884</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12071,12 +12065,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12085,6 +12079,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12102,16 +12097,16 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136618852</t>
+          <t>https://artportalen.se/Sighting/135457684</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136619024</v>
+        <v>135457690</v>
       </c>
       <c r="B109" t="n">
-        <v>99372</v>
+        <v>99293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12137,19 +12132,27 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>550531</v>
+        <v>550353</v>
       </c>
       <c r="R109" t="n">
-        <v>6994142</v>
+        <v>6993851</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12173,12 +12176,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12187,6 +12190,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12204,45 +12208,45 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136619024</t>
+          <t>https://artportalen.se/Sighting/135457690</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135457602</v>
+        <v>135457698</v>
       </c>
       <c r="B110" t="n">
-        <v>106433</v>
+        <v>99293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -12253,10 +12257,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>550445</v>
+        <v>550455</v>
       </c>
       <c r="R110" t="n">
-        <v>6993808</v>
+        <v>6994009</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12291,11 +12295,6 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Tillsammans med knärot.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12320,58 +12319,54 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135457602</t>
+          <t>https://artportalen.se/Sighting/135457698</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135466572</v>
+        <v>136618852</v>
       </c>
       <c r="B111" t="n">
-        <v>98161</v>
+        <v>99374</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>550481</v>
+        <v>550545</v>
       </c>
       <c r="R111" t="n">
-        <v>6993999</v>
+        <v>6994205</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12395,12 +12390,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12409,7 +12404,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12427,51 +12421,51 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135466572</t>
+          <t>https://artportalen.se/Sighting/136618852</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136618893</v>
+        <v>136619024</v>
       </c>
       <c r="B112" t="n">
-        <v>98240</v>
+        <v>99374</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>550520</v>
+        <v>550531</v>
       </c>
       <c r="R112" t="n">
-        <v>6994186</v>
+        <v>6994142</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12529,51 +12523,55 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136618893</t>
+          <t>https://artportalen.se/Sighting/136619024</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134246393</v>
+        <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99217</v>
+        <v>99374</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>550548</v>
+        <v>550482</v>
       </c>
       <c r="R113" t="n">
-        <v>6994192</v>
+        <v>6994003</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12600,12 +12598,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12614,33 +12612,34 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246393</t>
+          <t>https://artportalen.se/Sighting/137202010</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134246406</v>
+        <v>135457602</v>
       </c>
       <c r="B114" t="n">
-        <v>99217</v>
+        <v>106433</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12648,37 +12647,45 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221952</v>
+        <v>221144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>550277</v>
+        <v>550445</v>
       </c>
       <c r="R114" t="n">
-        <v>6994166</v>
+        <v>6993808</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12702,12 +12709,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Tillsammans med knärot.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12716,71 +12728,73 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246406</t>
+          <t>https://artportalen.se/Sighting/135457602</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126099623</v>
+        <v>135466572</v>
       </c>
       <c r="B115" t="n">
-        <v>79085</v>
+        <v>98161</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Skog vid Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
         <v>550481</v>
       </c>
       <c r="R115" t="n">
-        <v>6994133</v>
+        <v>6993999</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12807,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12839,51 +12853,51 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126099623</t>
+          <t>https://artportalen.se/Sighting/135466572</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134246390</v>
+        <v>136618893</v>
       </c>
       <c r="B116" t="n">
-        <v>79131</v>
+        <v>98242</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>550466</v>
+        <v>550520</v>
       </c>
       <c r="R116" t="n">
-        <v>6994147</v>
+        <v>6994186</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12910,12 +12924,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12930,65 +12944,65 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246390</t>
+          <t>https://artportalen.se/Sighting/136618893</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>136617473</v>
+        <v>134246393</v>
       </c>
       <c r="B117" t="n">
-        <v>79243</v>
+        <v>99217</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>550358</v>
+        <v>550548</v>
       </c>
       <c r="R117" t="n">
-        <v>6994160</v>
+        <v>6994192</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13012,12 +13026,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13032,62 +13046,62 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136617473</t>
+          <t>https://artportalen.se/Sighting/134246393</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136621098</v>
+        <v>134246406</v>
       </c>
       <c r="B118" t="n">
-        <v>79243</v>
+        <v>99217</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>550423</v>
+        <v>550277</v>
       </c>
       <c r="R118" t="n">
-        <v>6994020</v>
+        <v>6994166</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13114,12 +13128,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13134,27 +13148,27 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136621098</t>
+          <t>https://artportalen.se/Sighting/134246406</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>102089933</v>
+        <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>80392</v>
+        <v>101584</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13162,38 +13176,41 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>550373</v>
+        <v>550479</v>
       </c>
       <c r="R119" t="n">
-        <v>6994082</v>
+        <v>6993998</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13217,12 +13234,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13231,6 +13248,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13248,51 +13266,55 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102089933</t>
+          <t>https://artportalen.se/Sighting/137201951</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136620458</v>
+        <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>93457</v>
+        <v>99651</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>232140</v>
+        <v>222812</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>550496</v>
+        <v>550479</v>
       </c>
       <c r="R120" t="n">
-        <v>6994094</v>
+        <v>6993998</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13333,6 +13355,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13350,7 +13373,942 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137201954</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126099623</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Skog vid Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>550481</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6994133</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126099623</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>134246390</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>550466</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6994147</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246390</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>136617473</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>550358</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6994160</v>
+      </c>
+      <c r="S123" t="n">
+        <v>25</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136617473</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>136621098</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>550423</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6994020</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136621098</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>137201512</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>550442</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6993869</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137201512</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>102089933</v>
+      </c>
+      <c r="B126" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>550373</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6994082</v>
+      </c>
+      <c r="S126" t="n">
+        <v>25</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102089933</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>136620458</v>
+      </c>
+      <c r="B127" t="n">
+        <v>93457</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Blomkindtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>550496</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6994094</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136620458</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>121004368</v>
+      </c>
+      <c r="B128" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>550364</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6994169</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004368</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>121004446</v>
+      </c>
+      <c r="B129" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>550416</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6994077</v>
+      </c>
+      <c r="S129" t="n">
+        <v>25</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004446</t>
         </is>
       </c>
     </row>
@@ -13475,6 +14433,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2381,7 +2381,7 @@
         <v>136620821</v>
       </c>
       <c r="B18" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>136617608</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>136618272</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>136620831</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136617683</v>
       </c>
       <c r="B52" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>136618637</v>
       </c>
       <c r="B53" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136621169</v>
       </c>
       <c r="B54" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136617434</v>
       </c>
       <c r="B55" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136673687</v>
       </c>
       <c r="B58" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>136617444</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>136618852</v>
       </c>
       <c r="B111" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>136619024</v>
       </c>
       <c r="B112" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>136618893</v>
       </c>
       <c r="B116" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>136617473</v>
       </c>
       <c r="B123" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>136621098</v>
       </c>
       <c r="B124" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>136620458</v>
       </c>
       <c r="B127" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2381,7 +2381,7 @@
         <v>136620821</v>
       </c>
       <c r="B18" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>136617608</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>136618272</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>136620831</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136617683</v>
       </c>
       <c r="B52" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>136618637</v>
       </c>
       <c r="B53" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136621169</v>
       </c>
       <c r="B54" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136617434</v>
       </c>
       <c r="B55" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136673687</v>
       </c>
       <c r="B58" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>136617444</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136618720</v>
       </c>
       <c r="B85" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>136618852</v>
       </c>
       <c r="B111" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>136619024</v>
       </c>
       <c r="B112" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>136618893</v>
       </c>
       <c r="B116" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>136617473</v>
       </c>
       <c r="B123" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>136621098</v>
       </c>
       <c r="B124" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>136620458</v>
       </c>
       <c r="B127" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2381,7 +2381,7 @@
         <v>136620821</v>
       </c>
       <c r="B18" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>136617608</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>136618272</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>136620831</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136617683</v>
       </c>
       <c r="B52" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>136618637</v>
       </c>
       <c r="B53" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136621169</v>
       </c>
       <c r="B54" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136617434</v>
       </c>
       <c r="B55" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136673687</v>
       </c>
       <c r="B58" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>136617444</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>136618720</v>
       </c>
       <c r="B85" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>136618852</v>
       </c>
       <c r="B111" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>136619024</v>
       </c>
       <c r="B112" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>136618893</v>
       </c>
       <c r="B116" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>136617473</v>
       </c>
       <c r="B123" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>136621098</v>
       </c>
       <c r="B124" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>136620458</v>
       </c>
       <c r="B127" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -2381,7 +2381,7 @@
         <v>136620821</v>
       </c>
       <c r="B18" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>136617608</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>136618272</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>136620831</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>136617683</v>
       </c>
       <c r="B52" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>136618637</v>
       </c>
       <c r="B53" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>136621169</v>
       </c>
       <c r="B54" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>136617434</v>
       </c>
       <c r="B55" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136673687</v>
       </c>
       <c r="B58" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>136618852</v>
       </c>
       <c r="B111" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>136619024</v>
       </c>
       <c r="B112" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>136618893</v>
       </c>
       <c r="B116" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>136620458</v>
       </c>
       <c r="B127" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99671</v>
+        <v>99681</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99681</v>
+        <v>99682</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89384</v>
+        <v>89387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 41411-2024 artfynd.xlsx
+++ b/artfynd/A 41411-2024 artfynd.xlsx
@@ -5390,7 +5390,7 @@
         <v>137201461</v>
       </c>
       <c r="B46" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>137201516</v>
       </c>
       <c r="B47" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>137202122</v>
       </c>
       <c r="B57" t="n">
-        <v>89404</v>
+        <v>89407</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>137201958</v>
       </c>
       <c r="B89" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137202010</v>
       </c>
       <c r="B113" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>137201951</v>
       </c>
       <c r="B119" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>137201954</v>
       </c>
       <c r="B120" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>137201512</v>
       </c>
       <c r="B125" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>121004368</v>
       </c>
       <c r="B128" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>121004446</v>
       </c>
       <c r="B129" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
